--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109652</v>
+        <v>109656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109656</v>
+        <v>109659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109659</v>
+        <v>109660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109660</v>
+        <v>109677</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109693</v>
+        <v>109696</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129884460</v>
       </c>
       <c r="B2" t="n">
-        <v>109696</v>
+        <v>109783</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129884460</v>
+        <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109783</v>
+        <v>109997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -704,13 +704,9 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tofta-Visby, Gtl</t>
+          <t>Gotland (västra), Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -720,7 +716,7 @@
         <v>6384823</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -747,19 +743,9 @@
           <t>2024-07-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>09:21</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>09:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -773,7 +759,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109997</v>
+        <v>109999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109999</v>
+        <v>109991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109991</v>
+        <v>109992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109992</v>
+        <v>109990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109990</v>
+        <v>109991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109991</v>
+        <v>109997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>109997</v>
+        <v>110004</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131598003</v>
       </c>
       <c r="B2" t="n">
-        <v>110004</v>
+        <v>110009</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131598003</v>
+        <v>118765522</v>
       </c>
       <c r="B2" t="n">
-        <v>110012</v>
+        <v>99153</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220299</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gotland (västra), Gtl</t>
+          <t>Stenkumla, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>694289</v>
+        <v>694263</v>
       </c>
       <c r="R2" t="n">
-        <v>6384823</v>
+        <v>6384576</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Fåtalig</t>
+          <t>2024-06-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +764,428 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kaj Svahn</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118765620</v>
+      </c>
+      <c r="B3" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>694449</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6384814</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131598003</v>
+      </c>
+      <c r="B4" t="n">
+        <v>110159</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Gotland (västra), Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>694289</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6384823</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fåtalig</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Sofie Alveteg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Mikael Molander</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118765660</v>
+      </c>
+      <c r="B5" t="n">
+        <v>106140</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221137</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Majviva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Primula farinosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>694136</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6384739</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118765726</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenkumla, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>694414</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6384587</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Stenkumla</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-13</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Johan Engström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44304-2021 artfynd.xlsx
+++ b/artfynd/A 44304-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765522</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -878,6 +888,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765620</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131598003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1085,6 +1105,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765660</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1186,8 +1211,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118765726</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>